--- a/problems/general/3.contract_expiry_tracking/eval/answer_key/2_만료대상_정답.xlsx
+++ b/problems/general/3.contract_expiry_tracking/eval/answer_key/2_만료대상_정답.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="대상목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대상목록" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>data/contract_ledger_given.xlsx (★제공된 정답 계약대장). 1단계 추출을 틀려도 2단계는 영향 없음</t>
+          <t>데이터/1_계약대장_제출용.xlsx (1단계에서 본인이 채운 계약대장). 거기 적은 종료일·자동갱신·갱신통지일을 보고 고른다</t>
         </is>
       </c>
     </row>
